--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00764B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00764B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A10AFC01-5223-4FBA-98BA-1965AB14704A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1CD0BF5-6A13-4152-9AB4-25041998531B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FAC353D5-DD89-4D29-A887-226E448923D4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{08D4D5D2-0C44-41AF-8440-927385D0992D}"/>
   </bookViews>
   <sheets>
     <sheet name="00764B-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1544,25 +1544,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0316B5E5-D981-41FB-8590-6F269020F071}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745796AA-C0ED-43A7-91DB-F7D572CA34EA}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1716,7 +1716,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2019</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>25</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39" t="s">
         <v>67</v>
       </c>
